--- a/testdata/SauceDemoTestData.xlsx
+++ b/testdata/SauceDemoTestData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SauceDemoPlaywrightFramework - Copy\testdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SauceDemoPlaywrightFramework\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76AB78E6-C05D-4D33-827A-294A35CE05AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E6898DB-AC99-4471-A823-6A6E70AD2192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="3900" windowWidth="17280" windowHeight="8880" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TestData" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1639" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="366">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -1171,8 +1171,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5890,8 +5891,8 @@
       <c r="D2" t="s">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
-        <v>362</v>
+      <c r="E2" s="1">
+        <v>1234</v>
       </c>
       <c r="F2" t="s">
         <v>363</v>
@@ -6408,7 +6409,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:N3 A5:N13 A4:D4 F4:N4" numberStoredAsText="1"/>
+    <ignoredError sqref="A3:N3 A5:N13 A4:D4 F4:N4 F1:N1 F2:N2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
